--- a/xlsx/carteira_mensal/Ago_2026.xlsx
+++ b/xlsx/carteira_mensal/Ago_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -174,7 +174,7 @@
     <t>Mirza Castelo Branco de Luca</t>
   </si>
   <si>
-    <t>Indicação de Amigo</t>
+    <t>Indicação de outros clientes</t>
   </si>
   <si>
     <t>04/08/26</t>
@@ -273,9 +273,6 @@
     <t>ADRIANA REGO BARROS MAGALHÃES</t>
   </si>
   <si>
-    <t>Cliente de porta</t>
-  </si>
-  <si>
     <t>Victor Costa</t>
   </si>
   <si>
@@ -303,10 +300,16 @@
     <t>Alexandre Gleyson Araujo da Silva</t>
   </si>
   <si>
+    <t>31/08/26</t>
+  </si>
+  <si>
+    <t>Márcia Elias Abucham</t>
+  </si>
+  <si>
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -315,28 +318,28 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.92</t>
+    <t>1.93</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>714.535,53</t>
-  </si>
-  <si>
-    <t>578.179,00</t>
+    <t>711.502,66</t>
+  </si>
+  <si>
+    <t>578.479,00</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>466.631,53</t>
+    <t>466.931,53</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>461.277,50</t>
+    <t>461.577,50</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
@@ -348,7 +351,7 @@
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>28.123,97</t>
+    <t>28.303,97</t>
   </si>
 </sst>
 </file>
@@ -417,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O60"/>
+  <dimension ref="A2:O61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -1330,7 +1333,7 @@
         <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="C45" t="n">
         <v>961.0</v>
@@ -1339,16 +1342,16 @@
         <v>81</v>
       </c>
       <c r="E45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G45" t="s">
         <v>87</v>
       </c>
-      <c r="F45" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>88</v>
-      </c>
-      <c r="H45" t="s">
-        <v>89</v>
       </c>
       <c r="I45" t="n">
         <v>24990.0</v>
@@ -1369,12 +1372,12 @@
         <v>96101.0</v>
       </c>
       <c r="O45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
         <v>76</v>
@@ -1383,7 +1386,7 @@
         <v>968.0</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
         <v>49</v>
@@ -1395,7 +1398,7 @@
         <v>50</v>
       </c>
       <c r="H46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I46" t="n">
         <v>281.69</v>
@@ -1416,12 +1419,12 @@
         <v>96801.0</v>
       </c>
       <c r="O46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
         <v>60</v>
@@ -1430,7 +1433,7 @@
         <v>973.0</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
         <v>61</v>
@@ -1442,7 +1445,7 @@
         <v>50</v>
       </c>
       <c r="H47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I47" t="n">
         <v>915.0</v>
@@ -1463,15 +1466,15 @@
         <v>97301.0</v>
       </c>
       <c r="O47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="C48" t="n">
         <v>976.0</v>
@@ -1480,13 +1483,13 @@
         <v>74</v>
       </c>
       <c r="E48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F48" t="n">
         <v>1.0</v>
       </c>
       <c r="G48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s">
         <v>82</v>
@@ -1515,7 +1518,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
         <v>72</v>
@@ -1536,7 +1539,7 @@
         <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I49" t="n">
         <v>63824.33</v>
@@ -1551,7 +1554,7 @@
         <v>52491.27</v>
       </c>
       <c r="M49" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="N49" t="n">
         <v>97401.0</v>
@@ -1560,20 +1563,59 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
+    <row r="50">
+      <c r="A50" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>97</v>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="n">
+        <v>979.0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" t="s">
+        <v>95</v>
+      </c>
+      <c r="I50" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N50" t="n">
+        <v>97901.0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="54">
@@ -1581,20 +1623,20 @@
         <v>99</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>103</v>
@@ -1602,34 +1644,42 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B60" s="3" t="s">
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
         <v>111</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Ago_2026.xlsx
+++ b/xlsx/carteira_mensal/Ago_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="119">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/08/2026 até 31/08/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,6 +153,39 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Gabriel Possebon Viegas de Sousa</t>
+  </si>
+  <si>
+    <t>Porta</t>
+  </si>
+  <si>
+    <t>25/07/26</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>08/08/26</t>
+  </si>
+  <si>
+    <t>Carla Fernandes da Silva</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>31/07/26</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>01/08/26</t>
+  </si>
+  <si>
     <t>LUCIANA LOTITO SIUFI</t>
   </si>
   <si>
@@ -165,12 +198,6 @@
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
-    <t>08/08/26</t>
-  </si>
-  <si>
     <t>Mirza Castelo Branco de Luca</t>
   </si>
   <si>
@@ -180,9 +207,6 @@
     <t>04/08/26</t>
   </si>
   <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
     <t>07/08/26</t>
   </si>
   <si>
@@ -195,9 +219,6 @@
     <t>Gabriel mesquita Cavalcante</t>
   </si>
   <si>
-    <t>Porta</t>
-  </si>
-  <si>
     <t>RAYSSA BARBOSA SILVA</t>
   </si>
   <si>
@@ -216,9 +237,6 @@
     <t>EDUARDO CASULO ALVAREZ</t>
   </si>
   <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
     <t>Wilza Silva Zake</t>
   </si>
   <si>
@@ -309,7 +327,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>20</t>
+    <t>22</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -318,40 +336,40 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.93</t>
+    <t>1.92</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>711.502,66</t>
-  </si>
-  <si>
-    <t>578.479,00</t>
+    <t>791.788,89</t>
+  </si>
+  <si>
+    <t>647.456,26</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>466.931,53</t>
+    <t>518.843,86</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>461.577,50</t>
+    <t>513.489,83</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>111.547,47</t>
+    <t>128.612,40</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>28.303,97</t>
+    <t>31.206,77</t>
   </si>
 </sst>
 </file>
@@ -420,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O61"/>
+  <dimension ref="A2:O63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -548,15 +566,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -564,7 +582,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -572,7 +590,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +696,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>920.0</v>
+        <v>903.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -696,22 +714,22 @@
         <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>19816.15</v>
+        <v>41773.66</v>
       </c>
       <c r="J31" t="n">
-        <v>961.4</v>
+        <v>9519.38</v>
       </c>
       <c r="K31" t="n">
-        <v>18854.75</v>
+        <v>32254.28</v>
       </c>
       <c r="L31" t="n">
-        <v>18410.11</v>
+        <v>32254.28</v>
       </c>
       <c r="M31" t="n">
         <v>1.9</v>
       </c>
       <c r="N31" t="n">
-        <v>92001.0</v>
+        <v>90301.0</v>
       </c>
       <c r="O31" t="s">
         <v>51</v>
@@ -725,7 +743,7 @@
         <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>924.0</v>
+        <v>914.0</v>
       </c>
       <c r="D32" t="s">
         <v>54</v>
@@ -743,22 +761,22 @@
         <v>56</v>
       </c>
       <c r="I32" t="n">
-        <v>32500.0</v>
+        <v>27203.6</v>
       </c>
       <c r="J32" t="n">
-        <v>8413.2</v>
+        <v>7545.55</v>
       </c>
       <c r="K32" t="n">
-        <v>24086.8</v>
+        <v>19658.05</v>
       </c>
       <c r="L32" t="n">
-        <v>22948.38</v>
+        <v>19658.05</v>
       </c>
       <c r="M32" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="N32" t="n">
-        <v>92401.0</v>
+        <v>91401.0</v>
       </c>
       <c r="O32" t="s">
         <v>56</v>
@@ -769,16 +787,16 @@
         <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
-        <v>923.0</v>
+        <v>920.0</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -787,45 +805,45 @@
         <v>50</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I33" t="n">
-        <v>140000.0</v>
+        <v>19816.15</v>
       </c>
       <c r="J33" t="n">
-        <v>20372.73</v>
+        <v>961.4</v>
       </c>
       <c r="K33" t="n">
-        <v>119627.27</v>
+        <v>18854.75</v>
       </c>
       <c r="L33" t="n">
-        <v>116814.72</v>
+        <v>18410.11</v>
       </c>
       <c r="M33" t="n">
         <v>1.9</v>
       </c>
       <c r="N33" t="n">
-        <v>92301.0</v>
+        <v>92001.0</v>
       </c>
       <c r="O33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C34" t="n">
-        <v>922.0</v>
+        <v>924.0</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
         <v>1.0</v>
@@ -834,46 +852,46 @@
         <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I34" t="n">
-        <v>450.0</v>
+        <v>32500.0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0</v>
+        <v>8413.2</v>
       </c>
       <c r="K34" t="n">
-        <v>450.0</v>
+        <v>24086.8</v>
       </c>
       <c r="L34" t="n">
-        <v>450.0</v>
+        <v>22948.38</v>
       </c>
       <c r="M34" t="n">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="N34" t="n">
-        <v>92201.0</v>
+        <v>92401.0</v>
       </c>
       <c r="O34" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="n">
+        <v>923.0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" t="s">
         <v>60</v>
       </c>
-      <c r="C35" t="n">
-        <v>929.0</v>
-      </c>
-      <c r="D35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" t="s">
-        <v>49</v>
-      </c>
       <c r="F35" t="n">
         <v>1.0</v>
       </c>
@@ -881,45 +899,45 @@
         <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I35" t="n">
-        <v>96000.0</v>
+        <v>140000.0</v>
       </c>
       <c r="J35" t="n">
-        <v>24851.29</v>
+        <v>20372.73</v>
       </c>
       <c r="K35" t="n">
-        <v>71148.71</v>
+        <v>119627.27</v>
       </c>
       <c r="L35" t="n">
-        <v>71148.71</v>
+        <v>116814.72</v>
       </c>
       <c r="M35" t="n">
         <v>1.9</v>
       </c>
       <c r="N35" t="n">
-        <v>92901.0</v>
+        <v>92301.0</v>
       </c>
       <c r="O35" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C36" t="n">
-        <v>928.0</v>
+        <v>922.0</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -928,45 +946,45 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I36" t="n">
-        <v>27400.0</v>
+        <v>450.0</v>
       </c>
       <c r="J36" t="n">
-        <v>7092.97</v>
+        <v>0.0</v>
       </c>
       <c r="K36" t="n">
-        <v>20307.03</v>
+        <v>450.0</v>
       </c>
       <c r="L36" t="n">
-        <v>19348.61</v>
+        <v>450.0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.0</v>
+        <v>2.27</v>
       </c>
       <c r="N36" t="n">
-        <v>92801.0</v>
+        <v>92201.0</v>
       </c>
       <c r="O36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="n">
+        <v>929.0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" t="s">
         <v>60</v>
-      </c>
-      <c r="C37" t="n">
-        <v>937.0</v>
-      </c>
-      <c r="D37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" t="s">
-        <v>49</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
@@ -993,7 +1011,7 @@
         <v>1.9</v>
       </c>
       <c r="N37" t="n">
-        <v>93701.0</v>
+        <v>92901.0</v>
       </c>
       <c r="O37" t="s">
         <v>51</v>
@@ -1001,19 +1019,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" t="n">
+        <v>928.0</v>
+      </c>
+      <c r="D38" t="s">
         <v>64</v>
       </c>
-      <c r="C38" t="n">
-        <v>934.0</v>
-      </c>
-      <c r="D38" t="s">
-        <v>51</v>
-      </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
@@ -1022,45 +1040,45 @@
         <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I38" t="n">
-        <v>2364.64</v>
+        <v>27400.0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0</v>
+        <v>7092.97</v>
       </c>
       <c r="K38" t="n">
-        <v>2364.64</v>
+        <v>20307.03</v>
       </c>
       <c r="L38" t="n">
-        <v>2364.64</v>
+        <v>19348.61</v>
       </c>
       <c r="M38" t="n">
-        <v>2.03</v>
+        <v>2.0</v>
       </c>
       <c r="N38" t="n">
-        <v>93401.0</v>
+        <v>92801.0</v>
       </c>
       <c r="O38" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
       </c>
       <c r="C39" t="n">
-        <v>943.0</v>
+        <v>937.0</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
@@ -1069,45 +1087,45 @@
         <v>50</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I39" t="n">
-        <v>750.0</v>
+        <v>96000.0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0</v>
+        <v>24851.29</v>
       </c>
       <c r="K39" t="n">
-        <v>750.0</v>
+        <v>71148.71</v>
       </c>
       <c r="L39" t="n">
-        <v>750.0</v>
+        <v>71148.71</v>
       </c>
       <c r="M39" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="N39" t="n">
-        <v>94301.0</v>
+        <v>93701.0</v>
       </c>
       <c r="O39" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C40" t="n">
-        <v>944.0</v>
+        <v>934.0</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1116,45 +1134,45 @@
         <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I40" t="n">
-        <v>21000.0</v>
+        <v>2364.64</v>
       </c>
       <c r="J40" t="n">
-        <v>770.55</v>
+        <v>0.0</v>
       </c>
       <c r="K40" t="n">
-        <v>20229.45</v>
+        <v>2364.64</v>
       </c>
       <c r="L40" t="n">
-        <v>20229.45</v>
+        <v>2364.64</v>
       </c>
       <c r="M40" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="N40" t="n">
-        <v>94401.0</v>
+        <v>93401.0</v>
       </c>
       <c r="O40" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C41" t="n">
-        <v>949.0</v>
+        <v>943.0</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
@@ -1163,136 +1181,136 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I41" t="n">
-        <v>9068.26</v>
+        <v>750.0</v>
       </c>
       <c r="J41" t="n">
-        <v>493.45</v>
+        <v>0.0</v>
       </c>
       <c r="K41" t="n">
-        <v>8574.81</v>
+        <v>750.0</v>
       </c>
       <c r="L41" t="n">
-        <v>8574.81</v>
+        <v>750.0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="N41" t="n">
-        <v>94901.0</v>
+        <v>94301.0</v>
       </c>
       <c r="O41" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" t="n">
+        <v>944.0</v>
+      </c>
+      <c r="D42" t="s">
         <v>75</v>
       </c>
-      <c r="B42" t="s">
+      <c r="E42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" t="s">
         <v>76</v>
       </c>
-      <c r="C42" t="n">
-        <v>953.0</v>
-      </c>
-      <c r="D42" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" t="s">
-        <v>79</v>
-      </c>
       <c r="I42" t="n">
-        <v>600.0</v>
+        <v>21000.0</v>
       </c>
       <c r="J42" t="n">
-        <v>22.2</v>
+        <v>770.55</v>
       </c>
       <c r="K42" t="n">
-        <v>577.8</v>
+        <v>20229.45</v>
       </c>
       <c r="L42" t="n">
-        <v>577.8</v>
+        <v>20229.45</v>
       </c>
       <c r="M42" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="N42" t="n">
-        <v>95301.0</v>
+        <v>94401.0</v>
       </c>
       <c r="O42" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="n">
+        <v>949.0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" t="s">
         <v>80</v>
       </c>
-      <c r="B43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" t="n">
-        <v>965.0</v>
-      </c>
-      <c r="D43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G43" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" t="s">
-        <v>82</v>
-      </c>
       <c r="I43" t="n">
-        <v>29027.98</v>
+        <v>9068.26</v>
       </c>
       <c r="J43" t="n">
-        <v>7514.3</v>
+        <v>493.45</v>
       </c>
       <c r="K43" t="n">
-        <v>21513.68</v>
+        <v>8574.81</v>
       </c>
       <c r="L43" t="n">
-        <v>21513.68</v>
+        <v>8574.81</v>
       </c>
       <c r="M43" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="N43" t="n">
-        <v>96501.0</v>
+        <v>94901.0</v>
       </c>
       <c r="O43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" t="n">
+        <v>953.0</v>
+      </c>
+      <c r="D44" t="s">
         <v>83</v>
-      </c>
-      <c r="B44" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" t="n">
-        <v>964.0</v>
-      </c>
-      <c r="D44" t="s">
-        <v>81</v>
       </c>
       <c r="E44" t="s">
         <v>84</v>
@@ -1304,72 +1322,72 @@
         <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I44" t="n">
-        <v>4647.95</v>
+        <v>600.0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0</v>
+        <v>22.2</v>
       </c>
       <c r="K44" t="n">
-        <v>4647.95</v>
+        <v>577.8</v>
       </c>
       <c r="L44" t="n">
-        <v>4647.95</v>
+        <v>577.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.0</v>
+        <v>2.01</v>
       </c>
       <c r="N44" t="n">
-        <v>96401.0</v>
+        <v>95301.0</v>
       </c>
       <c r="O44" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C45" t="n">
-        <v>961.0</v>
+        <v>965.0</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="F45" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G45" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H45" t="s">
         <v>88</v>
       </c>
       <c r="I45" t="n">
-        <v>24990.0</v>
+        <v>29027.98</v>
       </c>
       <c r="J45" t="n">
-        <v>4193.09</v>
+        <v>7514.3</v>
       </c>
       <c r="K45" t="n">
-        <v>20796.91</v>
+        <v>21513.68</v>
       </c>
       <c r="L45" t="n">
-        <v>20796.91</v>
+        <v>21513.68</v>
       </c>
       <c r="M45" t="n">
         <v>1.9</v>
       </c>
       <c r="N45" t="n">
-        <v>96101.0</v>
+        <v>96501.0</v>
       </c>
       <c r="O45" t="s">
         <v>88</v>
@@ -1380,17 +1398,17 @@
         <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C46" t="n">
-        <v>968.0</v>
+        <v>964.0</v>
       </c>
       <c r="D46" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" t="s">
         <v>90</v>
       </c>
-      <c r="E46" t="s">
-        <v>49</v>
-      </c>
       <c r="F46" t="n">
         <v>1.0</v>
       </c>
@@ -1398,28 +1416,28 @@
         <v>50</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I46" t="n">
-        <v>281.69</v>
+        <v>4647.95</v>
       </c>
       <c r="J46" t="n">
         <v>0.0</v>
       </c>
       <c r="K46" t="n">
-        <v>281.69</v>
+        <v>4647.95</v>
       </c>
       <c r="L46" t="n">
-        <v>281.69</v>
+        <v>4647.95</v>
       </c>
       <c r="M46" t="n">
         <v>3.0</v>
       </c>
       <c r="N46" t="n">
-        <v>96801.0</v>
+        <v>96401.0</v>
       </c>
       <c r="O46" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
@@ -1427,110 +1445,110 @@
         <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C47" t="n">
-        <v>973.0</v>
+        <v>961.0</v>
       </c>
       <c r="D47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G47" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I47" t="n">
-        <v>915.0</v>
+        <v>24990.0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0</v>
+        <v>4193.09</v>
       </c>
       <c r="K47" t="n">
-        <v>915.0</v>
+        <v>20796.91</v>
       </c>
       <c r="L47" t="n">
-        <v>915.0</v>
+        <v>20796.91</v>
       </c>
       <c r="M47" t="n">
-        <v>2.0</v>
+        <v>1.9</v>
       </c>
       <c r="N47" t="n">
-        <v>97301.0</v>
+        <v>96101.0</v>
       </c>
       <c r="O47" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" t="n">
+        <v>968.0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" t="s">
         <v>60</v>
       </c>
-      <c r="C48" t="n">
-        <v>976.0</v>
-      </c>
-      <c r="D48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" t="s">
-        <v>86</v>
-      </c>
       <c r="F48" t="n">
         <v>1.0</v>
       </c>
       <c r="G48" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I48" t="n">
-        <v>8543.0</v>
+        <v>281.69</v>
       </c>
       <c r="J48" t="n">
-        <v>677.94</v>
+        <v>0.0</v>
       </c>
       <c r="K48" t="n">
-        <v>7865.06</v>
+        <v>281.69</v>
       </c>
       <c r="L48" t="n">
-        <v>7865.06</v>
+        <v>281.69</v>
       </c>
       <c r="M48" t="n">
-        <v>1.83</v>
+        <v>3.0</v>
       </c>
       <c r="N48" t="n">
-        <v>97601.0</v>
+        <v>96801.0</v>
       </c>
       <c r="O48" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>973.0</v>
+      </c>
+      <c r="D49" t="s">
         <v>94</v>
       </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="n">
-        <v>974.0</v>
-      </c>
-      <c r="D49" t="s">
-        <v>74</v>
-      </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F49" t="n">
         <v>1.0</v>
@@ -1539,147 +1557,241 @@
         <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I49" t="n">
-        <v>63824.33</v>
+        <v>915.0</v>
       </c>
       <c r="J49" t="n">
-        <v>11333.06</v>
+        <v>0.0</v>
       </c>
       <c r="K49" t="n">
-        <v>52491.27</v>
+        <v>915.0</v>
       </c>
       <c r="L49" t="n">
-        <v>52491.27</v>
+        <v>915.0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.05</v>
+        <v>2.0</v>
       </c>
       <c r="N49" t="n">
-        <v>97401.0</v>
+        <v>97301.0</v>
       </c>
       <c r="O49" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
         <v>47</v>
       </c>
       <c r="C50" t="n">
+        <v>976.0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8543.0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>677.94</v>
+      </c>
+      <c r="K50" t="n">
+        <v>7865.06</v>
+      </c>
+      <c r="L50" t="n">
+        <v>7865.06</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N50" t="n">
+        <v>97601.0</v>
+      </c>
+      <c r="O50" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" t="n">
+        <v>974.0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I51" t="n">
+        <v>63824.33</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11333.06</v>
+      </c>
+      <c r="K51" t="n">
+        <v>52491.27</v>
+      </c>
+      <c r="L51" t="n">
+        <v>52491.27</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N51" t="n">
+        <v>97401.0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="n">
         <v>979.0</v>
       </c>
-      <c r="D50" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="D52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" t="n">
         <v>5.0</v>
       </c>
-      <c r="G50" t="s">
-        <v>50</v>
-      </c>
-      <c r="H50" t="s">
-        <v>95</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="G52" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" t="s">
+        <v>101</v>
+      </c>
+      <c r="I52" t="n">
         <v>300.0</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J52" t="n">
         <v>0.0</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K52" t="n">
         <v>300.0</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L52" t="n">
         <v>300.0</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M52" t="n">
         <v>2.42</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N52" t="n">
         <v>97901.0</v>
       </c>
-      <c r="O50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>98</v>
+      <c r="O52" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Ago_2026.xlsx
+++ b/xlsx/carteira_mensal/Ago_2026.xlsx
@@ -195,7 +195,7 @@
     <t>03/08/26</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>Mirza Castelo Branco de Luca</t>
